--- a/artfynd/A 5135-2021 artfynd.xlsx
+++ b/artfynd/A 5135-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124191</v>
       </c>
       <c r="B2" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5135-2021 artfynd.xlsx
+++ b/artfynd/A 5135-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124191</v>
       </c>
       <c r="B2" t="n">
-        <v>58532</v>
+        <v>58544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5135-2021 artfynd.xlsx
+++ b/artfynd/A 5135-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128124191</v>
       </c>
       <c r="B2" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
